--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2635898F-02E1-124C-B9D6-B2B24C50A641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA227730-7821-3643-8E8E-32BCAEC0486C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{89336E3A-1883-E347-B030-FA5F11EBFB7D}"/>
   </bookViews>
@@ -689,7 +689,7 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
         <v>32</v>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA227730-7821-3643-8E8E-32BCAEC0486C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00823A03-C816-7144-A842-E7E80EDE2F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{89336E3A-1883-E347-B030-FA5F11EBFB7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Plant</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>OLPN;OLPN</t>
+  </si>
+  <si>
+    <t>VAS Codes</t>
   </si>
 </sst>
 </file>
@@ -167,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,18 +179,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -219,26 +234,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -594,22 +644,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="4" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="5"/>
       <c r="M1" s="6" t="s">
         <v>18</v>
       </c>
@@ -732,10 +784,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="I1:L1"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="M1:R1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R3" r:id="rId1" xr:uid="{7CB6C3CD-ECBD-4540-8AD5-082B6EFF93C8}"/>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00823A03-C816-7144-A842-E7E80EDE2F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1F95F0-87BD-4845-B818-E38D86126B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{89336E3A-1883-E347-B030-FA5F11EBFB7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Plant</t>
   </si>
@@ -134,19 +134,16 @@
     <t>Z011</t>
   </si>
   <si>
-    <t>BQ3204-400-8;BQ3204-400-8</t>
-  </si>
-  <si>
-    <t>15;30</t>
-  </si>
-  <si>
-    <t>BOX;BOX</t>
-  </si>
-  <si>
-    <t>OLPN;OLPN</t>
-  </si>
-  <si>
     <t>VAS Codes</t>
+  </si>
+  <si>
+    <t>BQ3204-400-8</t>
+  </si>
+  <si>
+    <t>BOX@LBL</t>
+  </si>
+  <si>
+    <t>OLPN@ITEM</t>
   </si>
 </sst>
 </file>
@@ -270,10 +267,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -288,7 +282,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -644,32 +641,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="6" t="s">
+      <c r="J1" s="8"/>
+      <c r="K1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="10"/>
+      <c r="M1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -741,13 +738,13 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
         <v>33</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
@@ -758,10 +755,10 @@
       <c r="J3" t="s">
         <v>13</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="M3" t="s">
@@ -792,6 +789,8 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R3" r:id="rId1" xr:uid="{7CB6C3CD-ECBD-4540-8AD5-082B6EFF93C8}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{D539E67F-7CA4-1E4E-BB66-7E7579E08B28}"/>
+    <hyperlink ref="L3" r:id="rId3" xr:uid="{D94C0C11-84E5-DE41-8683-329A84092585}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1F95F0-87BD-4845-B818-E38D86126B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2D1391-76E7-4D44-9674-ECADA3539C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{89336E3A-1883-E347-B030-FA5F11EBFB7D}"/>
+    <workbookView xWindow="47820" yWindow="3820" windowWidth="36000" windowHeight="22500" xr2:uid="{89336E3A-1883-E347-B030-FA5F11EBFB7D}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2D1391-76E7-4D44-9674-ECADA3539C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE0AB48-7A0A-8A4D-837E-DA4B3FCC8F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="47820" yWindow="3820" windowWidth="36000" windowHeight="22500" xr2:uid="{89336E3A-1883-E347-B030-FA5F11EBFB7D}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
+    <sheet name="BackUp" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
   <si>
     <t>Plant</t>
   </si>
@@ -68,9 +69,6 @@
     <t>VG</t>
   </si>
   <si>
-    <t>0000314896</t>
-  </si>
-  <si>
     <t>Order Type</t>
   </si>
   <si>
@@ -137,20 +135,32 @@
     <t>VAS Codes</t>
   </si>
   <si>
-    <t>BQ3204-400-8</t>
-  </si>
-  <si>
     <t>BOX@LBL</t>
   </si>
   <si>
     <t>OLPN@ITEM</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>LBL</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>123456-001-TST</t>
+  </si>
+  <si>
+    <t>0008006063</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -166,8 +176,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,8 +215,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7C7AC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94DCF8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E6A2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -257,16 +298,101 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -286,6 +412,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -641,87 +794,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="7" t="s">
+      <c r="A1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="12"/>
+      <c r="K1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="14"/>
+      <c r="M1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -735,49 +888,46 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="L3" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
         <v>26</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
       </c>
       <c r="P3">
         <v>54643</v>
       </c>
       <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -789,8 +939,167 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R3" r:id="rId1" xr:uid="{7CB6C3CD-ECBD-4540-8AD5-082B6EFF93C8}"/>
-    <hyperlink ref="K3" r:id="rId2" xr:uid="{D539E67F-7CA4-1E4E-BB66-7E7579E08B28}"/>
-    <hyperlink ref="L3" r:id="rId3" xr:uid="{D94C0C11-84E5-DE41-8683-329A84092585}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C995C2CF-7578-EA40-9155-2806622E836E}">
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="19"/>
+      <c r="K1" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="21"/>
+      <c r="M1" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1081</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="6">
+        <v>12</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="6">
+        <v>314896</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="6">
+        <v>54643</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:R1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K3" r:id="rId1" display="mailto:BOX@LBL" xr:uid="{61E4CA1F-34BE-7A46-993F-628C240676AB}"/>
+    <hyperlink ref="L3" r:id="rId2" display="mailto:OLPN@ITEM" xr:uid="{1B2AD2DF-2975-324F-B897-3D34CDD7A79E}"/>
+    <hyperlink ref="R3" r:id="rId3" display="mailto:AA@AA.AA" xr:uid="{E49019B1-26FB-B140-B07A-D155D1A2F9B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE0AB48-7A0A-8A4D-837E-DA4B3FCC8F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE01796-7FC6-A149-AD78-4696532DDB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="47820" yWindow="3820" windowWidth="36000" windowHeight="22500" xr2:uid="{89336E3A-1883-E347-B030-FA5F11EBFB7D}"/>
   </bookViews>
@@ -891,7 +891,7 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
         <v>37</v>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -2,42 +2,40 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE01796-7FC6-A149-AD78-4696532DDB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7EB415-10C9-1747-A5B0-5AB7D1FDE94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47820" yWindow="3820" windowWidth="36000" windowHeight="22500" xr2:uid="{89336E3A-1883-E347-B030-FA5F11EBFB7D}"/>
+    <workbookView xWindow="64000" yWindow="4600" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
-    <sheet name="BackUp" sheetId="2" r:id="rId2"/>
+    <sheet name="MasterData" sheetId="2" r:id="rId2"/>
+    <sheet name="MasterInput" sheetId="3" r:id="rId3"/>
+    <sheet name="BackUp" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
+  <si>
+    <t>Main Fields</t>
+  </si>
+  <si>
+    <t>B2B Fields</t>
+  </si>
+  <si>
+    <t>VAS Codes</t>
+  </si>
+  <si>
+    <t>B2C Fields</t>
+  </si>
   <si>
     <t>Plant</t>
   </si>
@@ -48,19 +46,49 @@
     <t>Initial</t>
   </si>
   <si>
+    <t>Order Type</t>
+  </si>
+  <si>
     <t>Number of Orders</t>
   </si>
   <si>
+    <t>Item(s)</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
+    <t>Service Level</t>
+  </si>
+  <si>
     <t>D_Facility</t>
   </si>
   <si>
+    <t>PrePack Code</t>
+  </si>
+  <si>
+    <t>VAS Code Service ID</t>
+  </si>
+  <si>
     <t>VAS Code Service UOM</t>
   </si>
   <si>
-    <t>Service Level</t>
+    <t>Address1</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Email</t>
   </si>
   <si>
     <t>QA</t>
@@ -69,98 +97,65 @@
     <t>VG</t>
   </si>
   <si>
-    <t>Order Type</t>
+    <t>Z011</t>
+  </si>
+  <si>
+    <t>123456-001-TST</t>
   </si>
   <si>
     <t>NXD</t>
   </si>
   <si>
+    <t>0008006063</t>
+  </si>
+  <si>
+    <t>LBL</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>YYY</t>
+  </si>
+  <si>
+    <t>ZZZ</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>AA@AA.AA</t>
+  </si>
+  <si>
+    <t>OrderID</t>
+  </si>
+  <si>
+    <t>VGORD0924QA3040</t>
+  </si>
+  <si>
+    <t>VGORD0924QA9691</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
     <t>SK</t>
   </si>
   <si>
-    <t>PrePack Code</t>
-  </si>
-  <si>
-    <t>VAS Code Service ID</t>
-  </si>
-  <si>
-    <t>Item(s)</t>
-  </si>
-  <si>
-    <t>B2B Fields</t>
-  </si>
-  <si>
-    <t>B2C Fields</t>
-  </si>
-  <si>
-    <t>Main Fields</t>
-  </si>
-  <si>
-    <t>Address1</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>YYY</t>
-  </si>
-  <si>
-    <t>ZZZ</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>AA@AA.AA</t>
-  </si>
-  <si>
-    <t>Z011</t>
-  </si>
-  <si>
-    <t>VAS Codes</t>
-  </si>
-  <si>
     <t>BOX@LBL</t>
   </si>
   <si>
     <t>OLPN@ITEM</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>LBL</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>123456-001-TST</t>
-  </si>
-  <si>
-    <t>0008006063</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -182,6 +177,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="10">
@@ -240,7 +240,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -270,19 +270,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -341,19 +328,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -379,66 +353,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -775,9 +778,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B38D67-019E-934F-86EC-0149A9A3A0E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -793,61 +796,61 @@
     <col min="12" max="13" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="14"/>
-      <c r="M1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
+    <row r="1" spans="1:18">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="11"/>
+      <c r="K1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="11"/>
+      <c r="M1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -856,78 +859,78 @@
         <v>14</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1081</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="O3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P3">
         <v>54643</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -938,72 +941,129 @@
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{7CB6C3CD-ECBD-4540-8AD5-082B6EFF93C8}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C995C2CF-7578-EA40-9155-2806622E836E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="21"/>
-      <c r="M1" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
+    <row r="1" spans="1:18">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="17"/>
+      <c r="K1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="17"/>
+      <c r="M1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>13</v>
@@ -1012,94 +1072,94 @@
         <v>14</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" s="6">
         <v>1081</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E3" s="6">
         <v>1</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G3" s="6">
         <v>12</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I3" s="6">
         <v>314896</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="P3" s="6">
         <v>54643</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="M1:R1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:R1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K3" r:id="rId1" display="mailto:BOX@LBL" xr:uid="{61E4CA1F-34BE-7A46-993F-628C240676AB}"/>
-    <hyperlink ref="L3" r:id="rId2" display="mailto:OLPN@ITEM" xr:uid="{1B2AD2DF-2975-324F-B897-3D34CDD7A79E}"/>
-    <hyperlink ref="R3" r:id="rId3" display="mailto:AA@AA.AA" xr:uid="{E49019B1-26FB-B140-B07A-D155D1A2F9B5}"/>
+    <hyperlink ref="K3" r:id="rId1" display="mailto:BOX@LBL" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="L3" r:id="rId2" display="mailto:OLPN@ITEM" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="R3" r:id="rId3" display="mailto:AA@AA.AA" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -1,217 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7EB415-10C9-1747-A5B0-5AB7D1FDE94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="64000" yWindow="4600" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="56960" yWindow="3760" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
-    <sheet name="MasterData" sheetId="2" r:id="rId2"/>
-    <sheet name="MasterInput" sheetId="3" r:id="rId3"/>
-    <sheet name="BackUp" sheetId="4" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateOrder" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasterData" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasterInput" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BackUp" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
-  <si>
-    <t>Main Fields</t>
-  </si>
-  <si>
-    <t>B2B Fields</t>
-  </si>
-  <si>
-    <t>VAS Codes</t>
-  </si>
-  <si>
-    <t>B2C Fields</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Initial</t>
-  </si>
-  <si>
-    <t>Order Type</t>
-  </si>
-  <si>
-    <t>Number of Orders</t>
-  </si>
-  <si>
-    <t>Item(s)</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Service Level</t>
-  </si>
-  <si>
-    <t>D_Facility</t>
-  </si>
-  <si>
-    <t>PrePack Code</t>
-  </si>
-  <si>
-    <t>VAS Code Service ID</t>
-  </si>
-  <si>
-    <t>VAS Code Service UOM</t>
-  </si>
-  <si>
-    <t>Address1</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>VG</t>
-  </si>
-  <si>
-    <t>Z011</t>
-  </si>
-  <si>
-    <t>123456-001-TST</t>
-  </si>
-  <si>
-    <t>NXD</t>
-  </si>
-  <si>
-    <t>0008006063</t>
-  </si>
-  <si>
-    <t>LBL</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>YYY</t>
-  </si>
-  <si>
-    <t>ZZZ</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>AA@AA.AA</t>
-  </si>
-  <si>
-    <t>OrderID</t>
-  </si>
-  <si>
-    <t>VGORD0924QA3040</t>
-  </si>
-  <si>
-    <t>VGORD0924QA9691</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>BOX@LBL</t>
-  </si>
-  <si>
-    <t>OLPN@ITEM</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="10">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -240,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -398,67 +265,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -778,159 +744,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col width="5.33203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
+    <col width="5.83203125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+    <col width="9.83203125" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" style="13" min="5" max="5"/>
+    <col width="25.6640625" bestFit="1" customWidth="1" style="13" min="6" max="6"/>
+    <col width="8.1640625" bestFit="1" customWidth="1" style="13" min="7" max="7"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="13" min="8" max="8"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="13" min="11" max="11"/>
+    <col width="19.6640625" bestFit="1" customWidth="1" style="13" min="12" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="14" t="s">
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Main Fields</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>B2B Fields</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="n"/>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>VAS Codes</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="12" t="inlineStr">
+        <is>
+          <t>B2C Fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Initial</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Order Type</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Number of Orders</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Item(s)</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Service Level</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>D_Facility</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>PrePack Code</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>VAS Code Service ID</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>VAS Code Service UOM</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Address1</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>Postal Code</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ZP06</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>123456-001-TST</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3">
-        <v>54643</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>34</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NXD</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>0008006063</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>LBL</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Shop C70 Harbourtown</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Biggera Waters</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>4216</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>AA@AA.AA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -941,62 +974,93 @@
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <sheetData/>
+  <cols>
+    <col width="11.83203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
+    <col width="19.33203125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cretae Order</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Create Shipment</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Add Order to Shipment</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Add Spur to Run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>35</v>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>OrderID</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1081</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>81ORD1008QA1510</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1005,148 +1069,222 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="16" t="s">
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Main Fields</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>B2B Fields</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="n"/>
+      <c r="K1" s="21" t="inlineStr">
+        <is>
+          <t>VAS Codes</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="n"/>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t>B2C Fields</t>
+        </is>
+      </c>
+      <c r="N1" s="20" t="n"/>
+      <c r="O1" s="20" t="n"/>
+      <c r="P1" s="20" t="n"/>
+      <c r="Q1" s="20" t="n"/>
+      <c r="R1" s="20" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Initial</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Order Type</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Number of Orders</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Item(s)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Service Level</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>D_Facility</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>PrePack Code</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>VAS Code Service ID</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>VAS Code Service UOM</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Address1</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>Postal Code</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Z011</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="6">
-        <v>1081</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="6">
-        <v>12</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="6">
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>NXD</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
         <v>314896</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" s="6">
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>BOX@LBL</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>OLPN@ITEM</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>XXX</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>YYY</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="n">
         <v>54643</v>
       </c>
-      <c r="Q3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>34</v>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>AA@AA.AA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1157,9 +1295,9 @@
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K3" r:id="rId1" display="mailto:BOX@LBL" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="L3" r:id="rId2" display="mailto:OLPN@ITEM" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="R3" r:id="rId3" display="mailto:AA@AA.AA" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" display="mailto:BOX@LBL" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" display="mailto:OLPN@ITEM" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" display="mailto:AA@AA.AA" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="56960" yWindow="3760" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="880" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateOrder" sheetId="1" state="visible" r:id="rId1"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ZP06</t>
+          <t>Z014</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>123456-001-TST</t>
+          <t>DD9293-100-7</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -939,17 +939,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Shop C70 Harbourtown</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Biggera Waters</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="P3" t="n">

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB81F13-A040-1C44-AACA-6B94E555AAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CAF904-6886-6242-8D8D-959AAA619817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="56960" yWindow="8240" windowWidth="30240" windowHeight="19640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="56960" yWindow="8240" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -1,251 +1,86 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CAF904-6886-6242-8D8D-959AAA619817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="56960" yWindow="8240" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5760" yWindow="2920" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
-    <sheet name="CreateShipment" sheetId="5" r:id="rId2"/>
-    <sheet name="MasterData" sheetId="2" r:id="rId3"/>
-    <sheet name="MasterInput" sheetId="3" r:id="rId4"/>
-    <sheet name="BackUp" sheetId="4" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateOrder" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateShipment" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasterData" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasterInput" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BackUp" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipment_ID" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="53">
-  <si>
-    <t>Main Fields</t>
-  </si>
-  <si>
-    <t>B2B Fields</t>
-  </si>
-  <si>
-    <t>VAS Codes</t>
-  </si>
-  <si>
-    <t>B2C Fields</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Initial</t>
-  </si>
-  <si>
-    <t>Order Type</t>
-  </si>
-  <si>
-    <t>Number of Orders</t>
-  </si>
-  <si>
-    <t>Item(s)</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Service Level</t>
-  </si>
-  <si>
-    <t>D_Facility</t>
-  </si>
-  <si>
-    <t>PrePack Code</t>
-  </si>
-  <si>
-    <t>VAS Code Service ID</t>
-  </si>
-  <si>
-    <t>VAS Code Service UOM</t>
-  </si>
-  <si>
-    <t>Address1</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>Z014</t>
-  </si>
-  <si>
-    <t>DD9293-100-7</t>
-  </si>
-  <si>
-    <t>NXD</t>
-  </si>
-  <si>
-    <t>0008006063</t>
-  </si>
-  <si>
-    <t>LBL</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>BBB</t>
-  </si>
-  <si>
-    <t>CCC</t>
-  </si>
-  <si>
-    <t>AA@AA.AA</t>
-  </si>
-  <si>
-    <t>Cretae Order</t>
-  </si>
-  <si>
-    <t>Create Shipment</t>
-  </si>
-  <si>
-    <t>Add Order to Shipment</t>
-  </si>
-  <si>
-    <t>Add Spur to Run</t>
-  </si>
-  <si>
-    <t>OrderID</t>
-  </si>
-  <si>
-    <t>81ORD1013QA5490</t>
-  </si>
-  <si>
-    <t>VG</t>
-  </si>
-  <si>
-    <t>Z011</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>BOX@LBL</t>
-  </si>
-  <si>
-    <t>OLPN@ITEM</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>YYY</t>
-  </si>
-  <si>
-    <t>ZZZ</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Create_Shipment</t>
-  </si>
-  <si>
-    <t>Carrier</t>
-  </si>
-  <si>
-    <t>ServiceLevel</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="10">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -432,67 +267,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -812,159 +746,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col width="5.33203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
+    <col width="5.83203125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+    <col width="9.83203125" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" style="13" min="5" max="5"/>
+    <col width="25.6640625" bestFit="1" customWidth="1" style="13" min="6" max="6"/>
+    <col width="8.1640625" bestFit="1" customWidth="1" style="13" min="7" max="7"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="13" min="8" max="8"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="13" min="11" max="11"/>
+    <col width="19.6640625" bestFit="1" customWidth="1" style="13" min="12" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="14" t="s">
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Main Fields</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>B2B Fields</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="n"/>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>VAS Codes</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="12" t="inlineStr">
+        <is>
+          <t>B2C Fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Initial</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Order Type</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Number of Orders</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Item(s)</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Service Level</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>D_Facility</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>PrePack Code</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>VAS Code Service ID</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>VAS Code Service UOM</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Address1</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>Postal Code</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Z014</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DD9293-100-7</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3">
-        <v>1081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NXD</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>0008006063</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>LBL</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>4216</v>
       </c>
-      <c r="Q3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>32</v>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>AA@AA.AA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -975,51 +976,87 @@
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB4AE69-CDBB-5542-95A6-9D7BBFA7DA3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col width="5.33203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+    <col width="16.83203125" bestFit="1" customWidth="1" style="13" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" t="s">
-        <v>52</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Create_Shipment</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ServiceLevel</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1081</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>USPS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>USPS_FIRST_CLASS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PCL</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1028,33 +1065,47 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col width="11.83203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
+    <col width="19.33203125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" t="s">
-        <v>36</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cretae Order</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Create Shipment</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Add Order to Shipment</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Add Spur to Run</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>48</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1063,30 +1114,49 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col width="5.5" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>37</v>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>OrderID</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1081</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>81ORD1013QA5490</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1095,148 +1165,222 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="16" t="s">
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Main Fields</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>B2B Fields</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="n"/>
+      <c r="K1" s="21" t="inlineStr">
+        <is>
+          <t>VAS Codes</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="n"/>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t>B2C Fields</t>
+        </is>
+      </c>
+      <c r="N1" s="20" t="n"/>
+      <c r="O1" s="20" t="n"/>
+      <c r="P1" s="20" t="n"/>
+      <c r="Q1" s="20" t="n"/>
+      <c r="R1" s="20" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Initial</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Order Type</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Number of Orders</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Item(s)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Service Level</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>D_Facility</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>PrePack Code</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>VAS Code Service ID</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>VAS Code Service UOM</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Address1</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>Postal Code</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Z011</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="6">
-        <v>1081</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="6">
-        <v>12</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="6">
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>NXD</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
         <v>314896</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" s="6">
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>BOX@LBL</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>OLPN@ITEM</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>XXX</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>YYY</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="n">
         <v>54643</v>
       </c>
-      <c r="Q3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>32</v>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>AA@AA.AA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1247,10 +1391,56 @@
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K3" r:id="rId1" display="mailto:BOX@LBL" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="L3" r:id="rId2" display="mailto:OLPN@ITEM" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="R3" r:id="rId3" display="mailto:AA@AA.AA" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" display="mailto:BOX@LBL" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" display="mailto:OLPN@ITEM" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" display="mailto:AA@AA.AA" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>ShipmentId</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VGS101525119</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1081</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5760" yWindow="2920" windowWidth="30240" windowHeight="19640" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="34120" yWindow="500" windowWidth="34160" windowHeight="28300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateOrder" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasterInput" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BackUp" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipment_ID" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OriginalOrderInput" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -43,6 +44,11 @@
       <color rgb="FF000000"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -109,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -268,6 +274,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -309,7 +330,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -319,6 +340,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -350,7 +374,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -754,46 +778,46 @@
   <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="5.33203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
-    <col width="5.83203125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
-    <col width="9.83203125" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
-    <col width="15.33203125" bestFit="1" customWidth="1" style="13" min="5" max="5"/>
-    <col width="25.6640625" bestFit="1" customWidth="1" style="13" min="6" max="6"/>
-    <col width="8.1640625" bestFit="1" customWidth="1" style="13" min="7" max="7"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="13" min="8" max="8"/>
-    <col width="11.1640625" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
-    <col width="12.33203125" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
-    <col width="17.5" bestFit="1" customWidth="1" style="13" min="11" max="11"/>
-    <col width="19.6640625" bestFit="1" customWidth="1" style="13" min="12" max="13"/>
+    <col width="5.33203125" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="5.83203125" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
+    <col width="9.83203125" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
+    <col width="25.6640625" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
+    <col width="8.1640625" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="14" min="10" max="10"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="14" min="11" max="11"/>
+    <col width="19.6640625" bestFit="1" customWidth="1" style="14" min="12" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Main Fields</t>
         </is>
       </c>
-      <c r="B1" s="10" t="n"/>
-      <c r="C1" s="10" t="n"/>
-      <c r="D1" s="10" t="n"/>
-      <c r="E1" s="10" t="n"/>
-      <c r="F1" s="10" t="n"/>
-      <c r="G1" s="10" t="n"/>
-      <c r="H1" s="11" t="n"/>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
+      <c r="H1" s="12" t="n"/>
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>B2B Fields</t>
         </is>
       </c>
-      <c r="J1" s="11" t="n"/>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="J1" s="12" t="n"/>
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>VAS Codes</t>
         </is>
       </c>
-      <c r="L1" s="11" t="n"/>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="L1" s="12" t="n"/>
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>B2C Fields</t>
         </is>
@@ -901,7 +925,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +941,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -991,10 +1015,10 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="5.33203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
-    <col width="15.33203125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
-    <col width="16.83203125" bestFit="1" customWidth="1" style="13" min="5" max="5"/>
+    <col width="5.33203125" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
+    <col width="16.83203125" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1073,10 +1097,10 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="11.83203125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
-    <col width="14.83203125" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
-    <col width="19.33203125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
-    <col width="13.6640625" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
+    <col width="11.83203125" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="19.33203125" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1119,12 +1143,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="5.5" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
-    <col width="17.5" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
+    <col width="5.5" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="17.83203125" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,7 +1179,97 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ORD1013QA5490</t>
+          <t>VGORD1015QA4320</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VGORD1015QA9661</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VGORD1015QA6982</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VGORD1015QA9303</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VGORD1015QA1784</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VGORD1015QA9715</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VGORD1015QA3936</t>
         </is>
       </c>
     </row>
@@ -1174,40 +1288,40 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Main Fields</t>
         </is>
       </c>
-      <c r="B1" s="10" t="n"/>
-      <c r="C1" s="10" t="n"/>
-      <c r="D1" s="10" t="n"/>
-      <c r="E1" s="10" t="n"/>
-      <c r="F1" s="10" t="n"/>
-      <c r="G1" s="10" t="n"/>
-      <c r="H1" s="11" t="n"/>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
+      <c r="H1" s="12" t="n"/>
+      <c r="I1" s="17" t="inlineStr">
         <is>
           <t>B2B Fields</t>
         </is>
       </c>
-      <c r="J1" s="17" t="n"/>
-      <c r="K1" s="21" t="inlineStr">
+      <c r="J1" s="18" t="n"/>
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>VAS Codes</t>
         </is>
       </c>
-      <c r="L1" s="17" t="n"/>
-      <c r="M1" s="19" t="inlineStr">
+      <c r="L1" s="18" t="n"/>
+      <c r="M1" s="20" t="inlineStr">
         <is>
           <t>B2C Fields</t>
         </is>
       </c>
-      <c r="N1" s="20" t="n"/>
-      <c r="O1" s="20" t="n"/>
-      <c r="P1" s="20" t="n"/>
-      <c r="Q1" s="20" t="n"/>
-      <c r="R1" s="20" t="n"/>
+      <c r="N1" s="21" t="n"/>
+      <c r="O1" s="21" t="n"/>
+      <c r="P1" s="21" t="n"/>
+      <c r="Q1" s="21" t="n"/>
+      <c r="R1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1405,38 +1519,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>ShipmentId</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>Service_Level</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VGS101625842</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>USPS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>USPS_FIRST_CLASS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PCL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>ShipmentId</t>
-        </is>
-      </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>OrderID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>VGS101525119</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>1081</v>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>80ORD1016QA6210</t>
         </is>
       </c>
     </row>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F374000-07FF-BE4E-8CAD-E6D671E89376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD145FAF-AA13-3E40-9EAE-575779BF7029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2360" yWindow="2260" windowWidth="34140" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
   <si>
     <t>Main Fields</t>
   </si>
@@ -220,17 +220,20 @@
     <t>Service_Level</t>
   </si>
   <si>
-    <t>VGS102225821</t>
-  </si>
-  <si>
-    <t>VGORD1022QA2660</t>
+    <t>VGS103025116</t>
+  </si>
+  <si>
+    <t>VGORD1030QA6240</t>
+  </si>
+  <si>
+    <t>VGORD1030QA6511</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -252,6 +255,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
@@ -320,7 +328,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -460,6 +468,21 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -498,7 +521,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -511,6 +534,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -895,32 +921,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="15" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="16" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="13" t="s">
+      <c r="L1" s="13"/>
+      <c r="M1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
@@ -992,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H3" t="s">
         <v>26</v>
@@ -1245,32 +1271,32 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="17" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="18"/>
-      <c r="K1" s="22" t="s">
+      <c r="J1" s="19"/>
+      <c r="K1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="18"/>
-      <c r="M1" s="20" t="s">
+      <c r="L1" s="19"/>
+      <c r="M1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
@@ -1404,24 +1430,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1452,8 +1486,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="9" t="s">
@@ -1477,6 +1514,17 @@
         <v>65</v>
       </c>
     </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -937,13 +937,13 @@
       <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DD9293-100-7</t>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGS110425471</t>
+          <t>VGS111925960</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGORD1104QA5100</t>
+          <t>VGORD1119QA6500</t>
         </is>
       </c>
     </row>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,21 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE3A209-BD37-3346-847B-719D4DCCD49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA253A44-5527-DC4F-AAA5-DD949FB9E29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
-    <sheet name="CreateShipment" sheetId="2" r:id="rId2"/>
-    <sheet name="MasterData" sheetId="3" r:id="rId3"/>
-    <sheet name="MasterInput" sheetId="4" r:id="rId4"/>
-    <sheet name="BackUp" sheetId="5" r:id="rId5"/>
-    <sheet name="Shipment_ID" sheetId="6" r:id="rId6"/>
-    <sheet name="OriginalOrderInput" sheetId="7" r:id="rId7"/>
-    <sheet name="Parent_Order" sheetId="8" r:id="rId8"/>
+    <sheet name="CreateAssignSpur" sheetId="9" r:id="rId2"/>
+    <sheet name="CreateShipment" sheetId="2" r:id="rId3"/>
+    <sheet name="MasterData" sheetId="3" r:id="rId4"/>
+    <sheet name="MasterInput" sheetId="4" r:id="rId5"/>
+    <sheet name="BackUp" sheetId="5" r:id="rId6"/>
+    <sheet name="Shipment_ID" sheetId="6" r:id="rId7"/>
+    <sheet name="OriginalOrderInput" sheetId="7" r:id="rId8"/>
+    <sheet name="Parent_Order" sheetId="8" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -237,7 +251,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -259,6 +273,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
@@ -327,7 +346,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -467,6 +486,21 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -505,7 +539,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -518,6 +552,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -902,32 +939,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="15" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="16" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="13" t="s">
+      <c r="L1" s="13"/>
+      <c r="M1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
@@ -1053,6 +1090,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD9A33F-8F9B-FF4C-BBFA-5450C4C2E2DF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1108,7 +1154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1143,7 +1189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -1246,38 +1292,38 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="17" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="18"/>
-      <c r="K1" s="22" t="s">
+      <c r="J1" s="19"/>
+      <c r="K1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="18"/>
-      <c r="M1" s="20" t="s">
+      <c r="L1" s="19"/>
+      <c r="M1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
@@ -1407,10 +1453,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="9" t="s">
@@ -1450,38 +1504,6 @@
       </c>
       <c r="F2" t="s">
         <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1081</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1490,6 +1512,43 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -1500,13 +1559,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>65</v>
       </c>
     </row>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-31960" yWindow="-1940" windowWidth="31220" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-32820" yWindow="-3000" windowWidth="31220" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateOrder" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BackUp" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipment_ID" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OriginalOrderInput" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parent_Order" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MHE_Journal" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parent_Order" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -62,6 +63,18 @@
       <family val="2"/>
       <color theme="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -128,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -347,6 +360,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -388,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -411,6 +454,12 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -442,7 +491,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -846,52 +895,52 @@
   <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="5.33203125" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="5.83203125" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="9.83203125" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
-    <col width="15.33203125" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
-    <col width="25.6640625" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
-    <col width="8.1640625" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
-    <col width="11.1640625" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="12.33203125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
-    <col width="12.33203125" customWidth="1" style="23" min="11" max="14"/>
-    <col width="17.5" bestFit="1" customWidth="1" style="23" min="15" max="15"/>
-    <col width="19.6640625" bestFit="1" customWidth="1" style="23" min="16" max="17"/>
-    <col width="13.1640625" bestFit="1" customWidth="1" style="23" min="23" max="23"/>
+    <col width="5.33203125" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="5.83203125" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
+    <col width="9.83203125" bestFit="1" customWidth="1" style="25" min="4" max="4"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" style="25" min="5" max="5"/>
+    <col width="25.6640625" bestFit="1" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8.1640625" bestFit="1" customWidth="1" style="25" min="7" max="7"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="25" min="8" max="8"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" style="25" min="9" max="9"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="25" min="10" max="10"/>
+    <col width="12.33203125" customWidth="1" style="25" min="11" max="14"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="25" min="15" max="15"/>
+    <col width="19.6640625" bestFit="1" customWidth="1" style="25" min="16" max="17"/>
+    <col width="13.1640625" bestFit="1" customWidth="1" style="25" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Main Fields</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="21" t="n"/>
-      <c r="G1" s="21" t="n"/>
-      <c r="H1" s="19" t="n"/>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="B1" s="23" t="n"/>
+      <c r="C1" s="23" t="n"/>
+      <c r="D1" s="23" t="n"/>
+      <c r="E1" s="23" t="n"/>
+      <c r="F1" s="23" t="n"/>
+      <c r="G1" s="23" t="n"/>
+      <c r="H1" s="21" t="n"/>
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>B2B Fields</t>
         </is>
       </c>
-      <c r="J1" s="21" t="n"/>
-      <c r="K1" s="21" t="n"/>
-      <c r="L1" s="21" t="n"/>
-      <c r="M1" s="21" t="n"/>
-      <c r="N1" s="19" t="n"/>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="J1" s="23" t="n"/>
+      <c r="K1" s="23" t="n"/>
+      <c r="L1" s="23" t="n"/>
+      <c r="M1" s="23" t="n"/>
+      <c r="N1" s="21" t="n"/>
+      <c r="O1" s="20" t="inlineStr">
         <is>
           <t>VAS Codes</t>
         </is>
       </c>
-      <c r="P1" s="19" t="n"/>
-      <c r="Q1" s="22" t="inlineStr">
+      <c r="P1" s="21" t="n"/>
+      <c r="Q1" s="24" t="inlineStr">
         <is>
           <t>B2C Fields</t>
         </is>
@@ -1033,8 +1082,10 @@
           <t>Z003</t>
         </is>
       </c>
-      <c r="E3" s="13" t="n">
-        <v>1</v>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1043,7 +1094,7 @@
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
@@ -1137,6 +1188,59 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col width="5.5" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="10.1640625" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>OrderId</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>810000156</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1146,11 +1250,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
   <cols>
-    <col width="5.33203125" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="34.1640625" customWidth="1" style="23" min="3" max="3"/>
-    <col width="18.1640625" customWidth="1" style="23" min="4" max="4"/>
-    <col width="30.1640625" customWidth="1" style="23" min="5" max="5"/>
+    <col width="5.33203125" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="34.1640625" customWidth="1" style="25" min="3" max="3"/>
+    <col width="18.1640625" customWidth="1" style="25" min="4" max="4"/>
+    <col width="30.1640625" customWidth="1" style="25" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1215,10 +1319,10 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="5.33203125" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="15.33203125" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="16.83203125" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="5.33203125" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
+    <col width="16.83203125" bestFit="1" customWidth="1" style="25" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1297,10 +1401,10 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="11.83203125" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="14.83203125" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="19.33203125" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="13.6640625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="11.83203125" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="19.33203125" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1346,9 +1450,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="5.5" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="17.83203125" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="5.5" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="17.83203125" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1398,40 +1502,40 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Main Fields</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="21" t="n"/>
-      <c r="G1" s="21" t="n"/>
-      <c r="H1" s="19" t="n"/>
-      <c r="I1" s="25" t="inlineStr">
+      <c r="B1" s="23" t="n"/>
+      <c r="C1" s="23" t="n"/>
+      <c r="D1" s="23" t="n"/>
+      <c r="E1" s="23" t="n"/>
+      <c r="F1" s="23" t="n"/>
+      <c r="G1" s="23" t="n"/>
+      <c r="H1" s="21" t="n"/>
+      <c r="I1" s="27" t="inlineStr">
         <is>
           <t>B2B Fields</t>
         </is>
       </c>
-      <c r="J1" s="26" t="n"/>
-      <c r="K1" s="30" t="inlineStr">
+      <c r="J1" s="28" t="n"/>
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>VAS Codes</t>
         </is>
       </c>
-      <c r="L1" s="26" t="n"/>
-      <c r="M1" s="28" t="inlineStr">
+      <c r="L1" s="28" t="n"/>
+      <c r="M1" s="30" t="inlineStr">
         <is>
           <t>B2C Fields</t>
         </is>
       </c>
-      <c r="N1" s="29" t="n"/>
-      <c r="O1" s="29" t="n"/>
-      <c r="P1" s="29" t="n"/>
-      <c r="Q1" s="29" t="n"/>
-      <c r="R1" s="29" t="n"/>
+      <c r="N1" s="31" t="n"/>
+      <c r="O1" s="31" t="n"/>
+      <c r="P1" s="31" t="n"/>
+      <c r="Q1" s="31" t="n"/>
+      <c r="R1" s="31" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1724,32 +1828,32 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>ShipmentId</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>Carrier</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Service_Level</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
@@ -1766,7 +1870,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGS011226359</t>
+          <t>VGS011526895</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1800,17 +1904,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="31" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
@@ -1829,7 +1933,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ORD0113QA2910</t>
+          <t>8101208380</t>
         </is>
       </c>
     </row>
@@ -1844,49 +1948,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col width="5.5" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="10.1640625" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="5.5" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="11.6640625" customWidth="1" style="25" min="2" max="4"/>
+    <col width="8.6640625" bestFit="1" customWidth="1" style="25" min="5" max="5"/>
+    <col width="7.83203125" bestFit="1" customWidth="1" style="25" min="6" max="6"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>OrderId</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>810000156</t>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>iLPNs</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>oLPNs</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>OrderIDs</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>TaskIDs</t>
+        </is>
+      </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>WaveNumber</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B041B6-A90A-B547-A4A0-58801E7A65D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F6BBF8-148D-914C-A772-42E3632C5007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="600" windowWidth="36000" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37100" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="101">
   <si>
     <t>Main Fields</t>
   </si>
@@ -37,198 +37,207 @@
     <t>B2B Fields</t>
   </si>
   <si>
+    <t>B2C Fields</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Initial</t>
+  </si>
+  <si>
+    <t>Order Type</t>
+  </si>
+  <si>
+    <t>Number of Orders</t>
+  </si>
+  <si>
+    <t>Item(s)</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Service Level</t>
+  </si>
+  <si>
+    <t>D_Facility</t>
+  </si>
+  <si>
+    <t>Sold_Facility</t>
+  </si>
+  <si>
+    <t>CarrierCode</t>
+  </si>
+  <si>
+    <t>HUBCode</t>
+  </si>
+  <si>
+    <t>Route_nbr</t>
+  </si>
+  <si>
+    <t>Mark_for</t>
+  </si>
+  <si>
+    <t>Provider Service ID</t>
+  </si>
+  <si>
+    <t>VAS Code Service UOM</t>
+  </si>
+  <si>
+    <t>Address1</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Z003</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>899371-091-M</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>0005000049</t>
+  </si>
+  <si>
+    <t>0005000004</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>H401</t>
+  </si>
+  <si>
+    <t>CTL</t>
+  </si>
+  <si>
+    <t>oLPN</t>
+  </si>
+  <si>
+    <t>ADACHI-GUN</t>
+  </si>
+  <si>
+    <t>14-2 NAKANO MOTOMIYA-CHO</t>
+  </si>
+  <si>
+    <t>FUKUSHIMA</t>
+  </si>
+  <si>
+    <t>969-0073</t>
+  </si>
+  <si>
+    <t>NIKE STORE LE MARAIS</t>
+  </si>
+  <si>
+    <t>abc@gmail.com</t>
+  </si>
+  <si>
+    <t>+42124117814</t>
+  </si>
+  <si>
+    <t>MessageType</t>
+  </si>
+  <si>
+    <t>OrderID</t>
+  </si>
+  <si>
+    <t>WaveNumber</t>
+  </si>
+  <si>
+    <t>DCO_XNT_NIKEINT10MAWMOODROP</t>
+  </si>
+  <si>
+    <t>VGORD0107QA6550</t>
+  </si>
+  <si>
+    <t>iLPNs</t>
+  </si>
+  <si>
+    <t>oLPNs</t>
+  </si>
+  <si>
+    <t>OrderIDs</t>
+  </si>
+  <si>
+    <t>TaskIDs</t>
+  </si>
+  <si>
+    <t>Create_Shipment</t>
+  </si>
+  <si>
+    <t>Carrier</t>
+  </si>
+  <si>
+    <t>ServiceLevel</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>LTL</t>
+  </si>
+  <si>
+    <t>Cretae Order</t>
+  </si>
+  <si>
+    <t>Create Shipment</t>
+  </si>
+  <si>
+    <t>Add Order to Shipment</t>
+  </si>
+  <si>
+    <t>Add Spur to Run</t>
+  </si>
+  <si>
+    <t>0160073012</t>
+  </si>
+  <si>
     <t>VAS Codes</t>
   </si>
   <si>
-    <t>B2C Fields</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Initial</t>
-  </si>
-  <si>
-    <t>Order Type</t>
-  </si>
-  <si>
-    <t>Number of Orders</t>
-  </si>
-  <si>
-    <t>Item(s)</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Service Level</t>
-  </si>
-  <si>
-    <t>D_Facility</t>
-  </si>
-  <si>
-    <t>Sold_Facility</t>
-  </si>
-  <si>
-    <t>CarrierCode</t>
-  </si>
-  <si>
-    <t>HUBCode</t>
-  </si>
-  <si>
-    <t>Route_nbr</t>
-  </si>
-  <si>
-    <t>Mark_for</t>
+    <t>PrePack Code</t>
   </si>
   <si>
     <t>VAS Code Service ID</t>
   </si>
   <si>
-    <t>VAS Code Service UOM</t>
-  </si>
-  <si>
-    <t>Address1</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>V1</t>
-  </si>
-  <si>
-    <t>Z003</t>
-  </si>
-  <si>
-    <t>899371-091-M</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>STD</t>
-  </si>
-  <si>
-    <t>0005000049</t>
-  </si>
-  <si>
-    <t>0005000004</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>H401</t>
-  </si>
-  <si>
-    <t>ADACHI-GUN</t>
-  </si>
-  <si>
-    <t>14-2 NAKANO MOTOMIYA-CHO</t>
-  </si>
-  <si>
-    <t>FUKUSHIMA</t>
-  </si>
-  <si>
-    <t>969-0073</t>
-  </si>
-  <si>
-    <t>NIKE STORE LE MARAIS</t>
-  </si>
-  <si>
-    <t>abc@gmail.com</t>
-  </si>
-  <si>
-    <t>+42124117814</t>
-  </si>
-  <si>
-    <t>MessageType</t>
-  </si>
-  <si>
-    <t>OrderID</t>
-  </si>
-  <si>
-    <t>oLPN</t>
-  </si>
-  <si>
-    <t>WaveNumber</t>
-  </si>
-  <si>
-    <t>DCO_XNT_NIKEINT10MAWMOODROP</t>
-  </si>
-  <si>
-    <t>VGORD0107QA6550</t>
-  </si>
-  <si>
-    <t>iLPNs</t>
-  </si>
-  <si>
-    <t>oLPNs</t>
-  </si>
-  <si>
-    <t>OrderIDs</t>
-  </si>
-  <si>
-    <t>TaskIDs</t>
-  </si>
-  <si>
-    <t>Create_Shipment</t>
-  </si>
-  <si>
-    <t>Carrier</t>
-  </si>
-  <si>
-    <t>ServiceLevel</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>LTL</t>
-  </si>
-  <si>
-    <t>Cretae Order</t>
-  </si>
-  <si>
-    <t>Create Shipment</t>
-  </si>
-  <si>
-    <t>Add Order to Shipment</t>
-  </si>
-  <si>
-    <t>Add Spur to Run</t>
-  </si>
-  <si>
-    <t>0160073012</t>
-  </si>
-  <si>
-    <t>PrePack Code</t>
-  </si>
-  <si>
     <t>VG</t>
   </si>
   <si>
@@ -316,43 +325,13 @@
     <t>1081</t>
   </si>
   <si>
-    <t>V101227160</t>
-  </si>
-  <si>
-    <t>V101222651</t>
+    <t>V101273850</t>
   </si>
   <si>
     <t>OrderId</t>
   </si>
   <si>
     <t>810000156</t>
-  </si>
-  <si>
-    <t>ABCD;EFGH</t>
-  </si>
-  <si>
-    <t>dfsaj</t>
-  </si>
-  <si>
-    <t>asf</t>
-  </si>
-  <si>
-    <t>aslfj</t>
-  </si>
-  <si>
-    <t>asljdfl</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>VAS</t>
-  </si>
-  <si>
-    <t>CTL</t>
-  </si>
-  <si>
-    <t>Provider Service ID</t>
   </si>
 </sst>
 </file>
@@ -472,7 +451,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -720,12 +699,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -753,10 +747,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -785,10 +780,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1124,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -1138,94 +1129,90 @@
     <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:23">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="22" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="20" t="s">
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-    </row>
-    <row r="2" spans="1:24">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="O2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="P2" s="34" t="s">
-        <v>107</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>19</v>
@@ -1245,28 +1232,25 @@
       <c r="V2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" s="13" customFormat="1" ht="17" customHeight="1">
+    </row>
+    <row r="3" spans="1:23" s="13" customFormat="1" ht="17" customHeight="1">
       <c r="A3" s="13">
         <v>1081</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>104</v>
       </c>
       <c r="F3" t="s">
         <v>30</v>
@@ -1296,45 +1280,42 @@
         <v>300818</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>46</v>
+        <v>38</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="U3" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="W3" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="X3" s="12" t="s">
         <v>43</v>
+      </c>
+      <c r="V3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="W3" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="O1:P1"/>
     <mergeCell ref="I1:N1"/>
-    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="W3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="V3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1352,24 +1333,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>5</v>
-      </c>
       <c r="C1" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1391,22 +1372,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>5</v>
-      </c>
       <c r="C1" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1414,13 +1395,13 @@
         <v>1081</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
@@ -1437,32 +1418,32 @@
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>5</v>
-      </c>
       <c r="C1" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1470,22 +1451,10 @@
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1506,22 +1475,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1529,10 +1498,10 @@
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
@@ -1541,7 +1510,7 @@
         <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1562,21 +1531,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1596,13 +1565,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>5</v>
-      </c>
       <c r="C1" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1610,10 +1579,10 @@
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1627,87 +1596,87 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="27" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="28"/>
-      <c r="K1" s="32" t="s">
+      <c r="J1" s="29"/>
+      <c r="K1" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="29"/>
+      <c r="M1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1715,125 +1684,125 @@
         <v>1081</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E3" s="6">
         <v>1</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G3" s="6">
         <v>12</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I3" s="6">
         <v>314896</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P3" s="6">
         <v>54643</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1859,22 +1828,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>5</v>
-      </c>
       <c r="C1" s="18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1882,10 +1851,10 @@
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
@@ -1894,7 +1863,7 @@
         <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1904,40 +1873,29 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>45</v>
+      <c r="C1" s="20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F6BBF8-148D-914C-A772-42E3632C5007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102EF478-4E57-CF4D-8884-E0B5A32EFE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37100" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37100" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="105">
   <si>
     <t>Main Fields</t>
   </si>
@@ -121,159 +121,171 @@
     <t>1</t>
   </si>
   <si>
-    <t>899371-091-M</t>
+    <t>343738-031-1.5Y</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>0005000004</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>H102</t>
+  </si>
+  <si>
+    <t>CTL</t>
+  </si>
+  <si>
+    <t>oLPN</t>
+  </si>
+  <si>
+    <t>ADACHI-GUN</t>
+  </si>
+  <si>
+    <t>14-2 NAKANO MOTOMIYA-CHO</t>
+  </si>
+  <si>
+    <t>FUKUSHIMA</t>
+  </si>
+  <si>
+    <t>969-0073</t>
+  </si>
+  <si>
+    <t>NIKE STORE LE MARAIS</t>
+  </si>
+  <si>
+    <t>abc@gmail.com</t>
+  </si>
+  <si>
+    <t>+42124117814</t>
+  </si>
+  <si>
+    <t>MessageType</t>
+  </si>
+  <si>
+    <t>OrderID</t>
+  </si>
+  <si>
+    <t>WaveNumber</t>
+  </si>
+  <si>
+    <t>DCO_XNT_NIKEINT10MAWMOODROP</t>
+  </si>
+  <si>
+    <t>VGORD0107QA6550</t>
+  </si>
+  <si>
+    <t>iLPNs</t>
+  </si>
+  <si>
+    <t>oLPNs</t>
+  </si>
+  <si>
+    <t>OrderIDs</t>
+  </si>
+  <si>
+    <t>TaskIDs</t>
+  </si>
+  <si>
+    <t>V101273850</t>
+  </si>
+  <si>
+    <t>Create_Shipment</t>
+  </si>
+  <si>
+    <t>Carrier</t>
+  </si>
+  <si>
+    <t>ServiceLevel</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>LTL</t>
+  </si>
+  <si>
+    <t>Cretae Order</t>
+  </si>
+  <si>
+    <t>Create Shipment</t>
+  </si>
+  <si>
+    <t>Add Order to Shipment</t>
+  </si>
+  <si>
+    <t>Add Spur to Run</t>
+  </si>
+  <si>
+    <t>0160073012</t>
+  </si>
+  <si>
+    <t>VAS Codes</t>
+  </si>
+  <si>
+    <t>PrePack Code</t>
+  </si>
+  <si>
+    <t>VAS Code Service ID</t>
+  </si>
+  <si>
+    <t>VG</t>
+  </si>
+  <si>
+    <t>Z011</t>
+  </si>
+  <si>
+    <t>924156-100-S</t>
+  </si>
+  <si>
+    <t>NXD</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>BOX@LBL</t>
+  </si>
+  <si>
+    <t>OLPN@ITEM</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>YYY</t>
+  </si>
+  <si>
+    <t>ZZZ</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>AA@AA.AA</t>
+  </si>
+  <si>
+    <t>378341-104-11.5</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>STD</t>
-  </si>
-  <si>
     <t>0005000049</t>
   </si>
   <si>
-    <t>0005000004</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
     <t>H401</t>
   </si>
   <si>
-    <t>CTL</t>
-  </si>
-  <si>
-    <t>oLPN</t>
-  </si>
-  <si>
-    <t>ADACHI-GUN</t>
-  </si>
-  <si>
-    <t>14-2 NAKANO MOTOMIYA-CHO</t>
-  </si>
-  <si>
-    <t>FUKUSHIMA</t>
-  </si>
-  <si>
-    <t>969-0073</t>
-  </si>
-  <si>
-    <t>NIKE STORE LE MARAIS</t>
-  </si>
-  <si>
-    <t>abc@gmail.com</t>
-  </si>
-  <si>
-    <t>+42124117814</t>
-  </si>
-  <si>
-    <t>MessageType</t>
-  </si>
-  <si>
-    <t>OrderID</t>
-  </si>
-  <si>
-    <t>WaveNumber</t>
-  </si>
-  <si>
-    <t>DCO_XNT_NIKEINT10MAWMOODROP</t>
-  </si>
-  <si>
-    <t>VGORD0107QA6550</t>
-  </si>
-  <si>
-    <t>iLPNs</t>
-  </si>
-  <si>
-    <t>oLPNs</t>
-  </si>
-  <si>
-    <t>OrderIDs</t>
-  </si>
-  <si>
-    <t>TaskIDs</t>
-  </si>
-  <si>
-    <t>Create_Shipment</t>
-  </si>
-  <si>
-    <t>Carrier</t>
-  </si>
-  <si>
-    <t>ServiceLevel</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>LTL</t>
-  </si>
-  <si>
-    <t>Cretae Order</t>
-  </si>
-  <si>
-    <t>Create Shipment</t>
-  </si>
-  <si>
-    <t>Add Order to Shipment</t>
-  </si>
-  <si>
-    <t>Add Spur to Run</t>
-  </si>
-  <si>
-    <t>0160073012</t>
-  </si>
-  <si>
-    <t>VAS Codes</t>
-  </si>
-  <si>
-    <t>PrePack Code</t>
-  </si>
-  <si>
-    <t>VAS Code Service ID</t>
-  </si>
-  <si>
-    <t>VG</t>
-  </si>
-  <si>
-    <t>Z011</t>
-  </si>
-  <si>
-    <t>924156-100-S</t>
-  </si>
-  <si>
-    <t>NXD</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>BOX@LBL</t>
-  </si>
-  <si>
-    <t>OLPN@ITEM</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>YYY</t>
-  </si>
-  <si>
-    <t>ZZZ</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>AA@AA.AA</t>
-  </si>
-  <si>
     <t>TranLog Meesage Types</t>
   </si>
   <si>
@@ -325,13 +337,13 @@
     <t>1081</t>
   </si>
   <si>
-    <t>V101273850</t>
-  </si>
-  <si>
     <t>OrderId</t>
   </si>
   <si>
-    <t>810000156</t>
+    <t>810000414</t>
+  </si>
+  <si>
+    <t>0160535200;0160148802</t>
   </si>
 </sst>
 </file>
@@ -367,11 +379,6 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
@@ -383,6 +390,11 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
@@ -731,23 +743,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1196,19 +1208,19 @@
       <c r="J2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>17</v>
       </c>
       <c r="P2" s="1" t="s">
@@ -1232,79 +1244,79 @@
       <c r="V2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="W2" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="13" customFormat="1" ht="17" customHeight="1">
-      <c r="A3" s="13">
+    <row r="3" spans="1:23" s="12" customFormat="1" ht="17" customHeight="1">
+      <c r="A3" s="12">
         <v>1081</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F3" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>33</v>
       </c>
       <c r="J3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="M3" s="12">
+        <v>203501</v>
+      </c>
+      <c r="N3" s="12">
+        <v>300818</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="13">
-        <v>203501</v>
-      </c>
-      <c r="N3" s="13">
-        <v>300818</v>
-      </c>
-      <c r="O3" s="14" t="s">
+      <c r="P3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="Q3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="R3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="S3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="T3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="U3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="V3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="V3" s="14" t="s">
+      <c r="W3" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1325,32 +1337,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>99</v>
+      <c r="C1" s="19" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1371,40 +1378,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="16" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="16">
+        <v>1081</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="17">
-        <v>1081</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1424,26 +1431,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>48</v>
+      <c r="G1" s="15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1454,7 +1461,7 @@
         <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1511,7 @@
         <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -1571,7 +1578,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1581,7 +1588,7 @@
       <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1592,10 +1599,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:23">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1630,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="32"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:23">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1679,7 +1686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:23">
       <c r="A3" s="6">
         <v>1081</v>
       </c>
@@ -1735,74 +1742,145 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="4" spans="1:23" ht="17" customHeight="1">
+      <c r="A4" s="12">
+        <v>1081</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M4" s="12">
+        <v>203501</v>
+      </c>
+      <c r="N4" s="12">
+        <v>300818</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1816,6 +1894,7 @@
     <hyperlink ref="K3" r:id="rId1" display="mailto:BOX@LBL" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
     <hyperlink ref="L3" r:id="rId2" display="mailto:OLPN@ITEM" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
     <hyperlink ref="R3" r:id="rId3" display="mailto:AA@AA.AA" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
+    <hyperlink ref="V4" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1827,22 +1906,22 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="18" t="s">
+      <c r="E1" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1854,10 +1933,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -1884,18 +1963,18 @@
         <v>4</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
-        <v>98</v>
+      <c r="C2" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102EF478-4E57-CF4D-8884-E0B5A32EFE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F44979-9DE0-D34B-A3A9-6855ADE55165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-37100" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,7 +343,7 @@
     <t>810000414</t>
   </si>
   <si>
-    <t>0160535200;0160148802</t>
+    <t>0160544800;0160504201;0160545000;0160124809;0160124810;0160545200;0160545400;</t>
   </si>
 </sst>
 </file>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F44979-9DE0-D34B-A3A9-6855ADE55165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9E8E51-90E2-B14B-9CC1-655836428433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-37100" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,7 +343,7 @@
     <t>810000414</t>
   </si>
   <si>
-    <t>0160544800;0160504201;0160545000;0160124809;0160124810;0160545200;0160545400;</t>
+    <t>0160561600</t>
   </si>
 </sst>
 </file>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9E8E51-90E2-B14B-9CC1-655836428433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F74E328-7F07-604B-827A-4D0FA2269FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37100" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37100" yWindow="600" windowWidth="36000" windowHeight="21000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,7 @@
     <t>810000414</t>
   </si>
   <si>
-    <t>0160561600</t>
+    <t>0160443601;0160213801;0160061806</t>
   </si>
 </sst>
 </file>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F74E328-7F07-604B-827A-4D0FA2269FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C59216B-21AA-D746-A70E-AA39D2B6EDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37100" yWindow="600" windowWidth="36000" windowHeight="21000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="74880" yWindow="-5240" windowWidth="36000" windowHeight="22600" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -193,9 +193,6 @@
     <t>TaskIDs</t>
   </si>
   <si>
-    <t>V101273850</t>
-  </si>
-  <si>
     <t>Create_Shipment</t>
   </si>
   <si>
@@ -226,9 +223,6 @@
     <t>Add Spur to Run</t>
   </si>
   <si>
-    <t>0160073012</t>
-  </si>
-  <si>
     <t>VAS Codes</t>
   </si>
   <si>
@@ -343,7 +337,13 @@
     <t>810000414</t>
   </si>
   <si>
-    <t>0160443601;0160213801;0160061806</t>
+    <t>0160576600</t>
+  </si>
+  <si>
+    <t>W03052026000000000007</t>
+  </si>
+  <si>
+    <t>0160412602;0160105604</t>
   </si>
 </sst>
 </file>
@@ -1346,18 +1346,18 @@
         <v>4</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1420,14 +1420,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.6640625" customWidth="1"/>
     <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1454,15 +1454,217 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2">
+      <c r="A2" s="12">
         <v>1081</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
-        <v>54</v>
-      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="12"/>
+      <c r="G2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1488,16 +1690,16 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>57</v>
-      </c>
-      <c r="F1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1508,7 +1710,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -1517,7 +1719,7 @@
         <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1538,21 +1740,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>63</v>
-      </c>
-      <c r="D1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1589,7 +1791,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1618,7 +1820,7 @@
       </c>
       <c r="J1" s="29"/>
       <c r="K1" s="33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L1" s="29"/>
       <c r="M1" s="31" t="s">
@@ -1659,10 +1861,10 @@
         <v>11</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>18</v>
@@ -1694,52 +1896,52 @@
         <v>26</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E3" s="6">
         <v>1</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G3" s="6">
         <v>12</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I3" s="6">
         <v>314896</v>
       </c>
       <c r="J3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="P3" s="6">
         <v>54643</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="17" customHeight="1">
@@ -1759,16 +1961,16 @@
         <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>33</v>
@@ -1777,7 +1979,7 @@
         <v>34</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M4" s="12">
         <v>203501</v>
@@ -1815,7 +2017,7 @@
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1825,62 +2027,62 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1913,16 +2115,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1933,7 +2135,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -1942,7 +2144,7 @@
         <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +2170,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,28 +8,41 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C59216B-21AA-D746-A70E-AA39D2B6EDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAB911E-72F3-D944-AF83-90CB843A8AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="74880" yWindow="-5240" windowWidth="36000" windowHeight="22600" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37480" yWindow="920" windowWidth="36000" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
     <sheet name="TranLog" sheetId="2" r:id="rId2"/>
     <sheet name="MHE_Journal" sheetId="3" r:id="rId3"/>
-    <sheet name="CreateShipment" sheetId="4" r:id="rId4"/>
-    <sheet name="MasterData" sheetId="5" r:id="rId5"/>
-    <sheet name="MasterInput" sheetId="6" r:id="rId6"/>
-    <sheet name="BackUp" sheetId="7" r:id="rId7"/>
-    <sheet name="Shipment_ID" sheetId="8" r:id="rId8"/>
-    <sheet name="OriginalOrderInput" sheetId="9" r:id="rId9"/>
+    <sheet name="OriginalOrderInput" sheetId="9" r:id="rId4"/>
+    <sheet name="CreateShipment" sheetId="4" r:id="rId5"/>
+    <sheet name="MasterData" sheetId="5" r:id="rId6"/>
+    <sheet name="MasterInput" sheetId="6" r:id="rId7"/>
+    <sheet name="BackUp" sheetId="7" r:id="rId8"/>
+    <sheet name="Shipment_ID" sheetId="8" r:id="rId9"/>
     <sheet name="Parent_Order" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="107">
   <si>
     <t>Main Fields</t>
   </si>
@@ -340,10 +353,16 @@
     <t>0160576600</t>
   </si>
   <si>
-    <t>W03052026000000000007</t>
-  </si>
-  <si>
-    <t>0160412602;0160105604</t>
+    <t>CTL@BOX</t>
+  </si>
+  <si>
+    <t>oLPN@oLPN;</t>
+  </si>
+  <si>
+    <t>0160550424;0160599218;0160191043;0160191040;0160191042;0160174405;0160191041</t>
+  </si>
+  <si>
+    <t>W03202026000000000010</t>
   </si>
 </sst>
 </file>
@@ -1291,11 +1310,11 @@
       <c r="N3" s="12">
         <v>300818</v>
       </c>
-      <c r="O3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>37</v>
+      <c r="O3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="Q3" s="14" t="s">
         <v>38</v>
@@ -1328,6 +1347,8 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="V3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="O3" r:id="rId2" xr:uid="{319D5DB3-AEFB-E64C-8296-534A8EDE7444}"/>
+    <hyperlink ref="P3" r:id="rId3" xr:uid="{1CD8333A-C62E-7D4B-8E19-7E13B00AD3F6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1465,7 +1486,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="12"/>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1672,6 +1693,41 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1727,7 +1783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1762,7 +1818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -1799,9 +1855,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -2083,6 +2139,11 @@
     <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -2150,36 +2211,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAB911E-72F3-D944-AF83-90CB843A8AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D3C270-7755-704C-9BD2-CA037B01D366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37480" yWindow="920" windowWidth="36000" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="70900" yWindow="-2940" windowWidth="36000" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="108">
   <si>
     <t>Main Fields</t>
   </si>
@@ -359,10 +359,13 @@
     <t>oLPN@oLPN;</t>
   </si>
   <si>
-    <t>0160550424;0160599218;0160191043;0160191040;0160191042;0160174405;0160191041</t>
-  </si>
-  <si>
     <t>W03202026000000000010</t>
+  </si>
+  <si>
+    <t>0576321102;0576316206;0576316207</t>
+  </si>
+  <si>
+    <t>W04022026000000000005</t>
   </si>
 </sst>
 </file>
@@ -1486,7 +1489,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="12"/>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1719,7 +1722,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2143,7 +2146,7 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D3C270-7755-704C-9BD2-CA037B01D366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A8347B-9889-5746-9335-FE91B8152F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="70900" yWindow="-2940" windowWidth="36000" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36000" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -362,17 +362,17 @@
     <t>W03202026000000000010</t>
   </si>
   <si>
-    <t>0576321102;0576316206;0576316207</t>
-  </si>
-  <si>
-    <t>W04022026000000000005</t>
+    <t>0576356401;0576356400</t>
+  </si>
+  <si>
+    <t>W04072026000000000015</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -427,6 +427,12 @@
       <b/>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -485,7 +491,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -748,12 +754,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -784,6 +801,13 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1169,35 +1193,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="23" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="25" t="s">
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
@@ -1697,10 +1721,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1715,15 +1739,18 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="23" t="s">
         <v>106</v>
       </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="C3" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1864,32 +1891,32 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="28" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="29"/>
-      <c r="K1" s="33" t="s">
+      <c r="J1" s="32"/>
+      <c r="K1" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="31" t="s">
+      <c r="L1" s="32"/>
+      <c r="M1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="3" t="s">

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A8347B-9889-5746-9335-FE91B8152F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A18AC37-D336-664F-8FE5-7BAE9DBED694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36000" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36000" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -362,10 +362,10 @@
     <t>W03202026000000000010</t>
   </si>
   <si>
-    <t>0576356401;0576356400</t>
-  </si>
-  <si>
-    <t>W04072026000000000015</t>
+    <t>W04082026000000000033</t>
+  </si>
+  <si>
+    <t>0576379601;0576379600</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1513,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="12"/>
       <c r="G2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1746,7 +1746,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">

--- a/J30/Input_files/Outbound_Worksheet.xlsx
+++ b/J30/Input_files/Outbound_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A18AC37-D336-664F-8FE5-7BAE9DBED694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301D200C-3804-0B41-92EE-6A464D5A9B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36000" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="50520" yWindow="-8120" windowWidth="36000" windowHeight="22600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOrder" sheetId="1" r:id="rId1"/>
@@ -362,10 +362,10 @@
     <t>W03202026000000000010</t>
   </si>
   <si>
-    <t>W04082026000000000033</t>
-  </si>
-  <si>
-    <t>0576379601;0576379600</t>
+    <t>0576443200</t>
+  </si>
+  <si>
+    <t>W04232026000000000010</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1513,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="12"/>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1746,7 +1746,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
